--- a/artfynd/A 61459-2024 artfynd.xlsx
+++ b/artfynd/A 61459-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119143055</v>
+        <v>119815554</v>
       </c>
       <c r="B2" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459592</v>
+        <v>459309</v>
       </c>
       <c r="R2" t="n">
-        <v>7071549</v>
+        <v>7072062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119143051</v>
+        <v>119815265</v>
       </c>
       <c r="B3" t="n">
-        <v>90578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459601</v>
+        <v>459314</v>
       </c>
       <c r="R3" t="n">
-        <v>7071523</v>
+        <v>7072067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119142972</v>
+        <v>119815417</v>
       </c>
       <c r="B4" t="n">
-        <v>79571</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459602</v>
+        <v>459310</v>
       </c>
       <c r="R4" t="n">
-        <v>7071477</v>
+        <v>7072064</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,21 +958,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>lodyta</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -998,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119142997</v>
+        <v>119815516</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2682</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459586</v>
+        <v>459414</v>
       </c>
       <c r="R5" t="n">
-        <v>7071481</v>
+        <v>7071991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,21 +1059,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>död rönn</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119143003</v>
+        <v>119142996</v>
       </c>
       <c r="B6" t="n">
-        <v>94309</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459683</v>
+        <v>459707</v>
       </c>
       <c r="R6" t="n">
-        <v>7071533</v>
+        <v>7071326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119143047</v>
+        <v>119143003</v>
       </c>
       <c r="B7" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459604</v>
+        <v>459683</v>
       </c>
       <c r="R7" t="n">
-        <v>7071473</v>
+        <v>7071533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1261,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>lodyta</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1326,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119143081</v>
+        <v>119143092</v>
       </c>
       <c r="B8" t="n">
-        <v>98239</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459619</v>
+        <v>459702</v>
       </c>
       <c r="R8" t="n">
-        <v>7071449</v>
+        <v>7071323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119143092</v>
+        <v>119143034</v>
       </c>
       <c r="B9" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459702</v>
+        <v>459593</v>
       </c>
       <c r="R9" t="n">
-        <v>7071323</v>
+        <v>7071524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119143076</v>
+        <v>119815253</v>
       </c>
       <c r="B10" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,34 +1494,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459578</v>
+        <v>459205</v>
       </c>
       <c r="R10" t="n">
-        <v>7071533</v>
+        <v>7072139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,21 +1564,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1649,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119143005</v>
+        <v>119143076</v>
       </c>
       <c r="B11" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,39 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459856</v>
+        <v>459578</v>
       </c>
       <c r="R11" t="n">
-        <v>7071496</v>
+        <v>7071533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,6 +1665,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1760,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119143066</v>
+        <v>119142997</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459637</v>
+        <v>459586</v>
       </c>
       <c r="R12" t="n">
-        <v>7071388</v>
+        <v>7071481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,6 +1771,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>död rönn</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1866,15 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119142996</v>
+        <v>119815341</v>
       </c>
       <c r="B13" t="n">
-        <v>94309</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1807,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459707</v>
+        <v>459308</v>
       </c>
       <c r="R13" t="n">
-        <v>7071326</v>
+        <v>7072062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,12 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1881,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,37 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119143034</v>
+        <v>119143047</v>
       </c>
       <c r="B14" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459593</v>
+        <v>459604</v>
       </c>
       <c r="R14" t="n">
-        <v>7071524</v>
+        <v>7071473</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,6 +1978,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>lodyta</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2078,15 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119143037</v>
+        <v>119143055</v>
       </c>
       <c r="B15" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,21 +2014,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459655</v>
+        <v>459592</v>
       </c>
       <c r="R15" t="n">
-        <v>7071327</v>
+        <v>7071549</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,15 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119143024</v>
+        <v>119815767</v>
       </c>
       <c r="B16" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,34 +2115,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gullrun, Jmt</t>
+          <t>Fjällflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459574</v>
+        <v>459308</v>
       </c>
       <c r="R16" t="n">
-        <v>7071503</v>
+        <v>7072062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,12 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,21 +2185,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>klen rönn</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2295,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119815262</v>
+        <v>119143024</v>
       </c>
       <c r="B17" t="n">
-        <v>58176</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2216,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459304</v>
+        <v>459574</v>
       </c>
       <c r="R17" t="n">
-        <v>7072087</v>
+        <v>7071503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,12 +2270,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,16 +2286,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>klen rönn</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2401,15 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119815417</v>
+        <v>119143005</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2322,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459310</v>
+        <v>459856</v>
       </c>
       <c r="R18" t="n">
-        <v>7072064</v>
+        <v>7071496</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,12 +2381,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,12 +2401,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2507,50 +2417,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119815265</v>
+        <v>119143066</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459314</v>
+        <v>459637</v>
       </c>
       <c r="R19" t="n">
-        <v>7072067</v>
+        <v>7071388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,12 +2482,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2597,12 +2502,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2613,15 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119815551</v>
+        <v>119815262</v>
       </c>
       <c r="B20" t="n">
-        <v>97834</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220093</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459512</v>
+        <v>459304</v>
       </c>
       <c r="R20" t="n">
-        <v>7071892</v>
+        <v>7072087</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,15 +2619,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119815341</v>
+        <v>119202609</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2735,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>219811</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459308</v>
+        <v>459823</v>
       </c>
       <c r="R21" t="n">
-        <v>7072062</v>
+        <v>7071630</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,12 +2684,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,31 +2704,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119815516</v>
+        <v>119202561</v>
       </c>
       <c r="B22" t="n">
-        <v>94539</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2727,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2682</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459414</v>
+        <v>459819</v>
       </c>
       <c r="R22" t="n">
-        <v>7071991</v>
+        <v>7071637</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,12 +2781,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,66 +2801,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815625</v>
+        <v>119143081</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459227</v>
+        <v>459619</v>
       </c>
       <c r="R23" t="n">
-        <v>7072105</v>
+        <v>7071449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,12 +2878,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,12 +2898,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3037,15 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119815767</v>
+        <v>119815551</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,21 +2925,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>220093</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459308</v>
+        <v>459512</v>
       </c>
       <c r="R24" t="n">
-        <v>7072062</v>
+        <v>7071892</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,50 +3015,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119815554</v>
+        <v>119143037</v>
       </c>
       <c r="B25" t="n">
-        <v>78624</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fjällflon, Jmt</t>
+          <t>Gullrun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459309</v>
+        <v>459655</v>
       </c>
       <c r="R25" t="n">
-        <v>7072062</v>
+        <v>7071327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,12 +3080,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,15 +3100,121 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119142972</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gullrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>459602</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071477</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 61459-2024 artfynd.xlsx
+++ b/artfynd/A 61459-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815554</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815265</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142996</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143034</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143076</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815341</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143047</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143055</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815767</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2414,6 +2499,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143005</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143066</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815262</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202609</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202561</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143081</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815551</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3113,6 +3233,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119143037</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3219,8 +3344,40 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119142972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>